--- a/data/trans_orig/DCD_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/DCD_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) en 2023</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25293</t>
+          <t>26585</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47636</t>
+          <t>47454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43563</t>
+          <t>43691</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63894</t>
+          <t>63906</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73571</t>
+          <t>74711</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103780</t>
+          <t>104456</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263807</t>
+          <t>263989</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286150</t>
+          <t>284858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225741</t>
+          <t>225729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246072</t>
+          <t>245944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>497297</t>
+          <t>496621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>527506</t>
+          <t>526366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49415</t>
+          <t>48670</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85673</t>
+          <t>81163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>129061</t>
+          <t>130543</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>164022</t>
+          <t>165480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>184060</t>
+          <t>185908</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>237190</t>
+          <t>236990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>432717</t>
+          <t>437227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>468975</t>
+          <t>469720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350947</t>
+          <t>349489</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>385908</t>
+          <t>384426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>796169</t>
+          <t>796369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>849299</t>
+          <t>847451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45934</t>
+          <t>45370</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70894</t>
+          <t>70275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91858</t>
+          <t>92077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119354</t>
+          <t>118246</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142628</t>
+          <t>143681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>180972</t>
+          <t>181003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>245156</t>
+          <t>245775</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>270116</t>
+          <t>270680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>229774</t>
+          <t>230882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257270</t>
+          <t>257051</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>484206</t>
+          <t>484175</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>522550</t>
+          <t>521497</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39616</t>
+          <t>39250</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67200</t>
+          <t>67491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63486</t>
+          <t>67062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137628</t>
+          <t>139108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,17 +1824,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>158582</t>
+          <t>158581</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121204</t>
+          <t>115579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187675</t>
+          <t>189743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>245357</t>
+          <t>245066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272941</t>
+          <t>273307</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>338090</t>
+          <t>336610</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>412232</t>
+          <t>408656</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>629692</t>
+          <t>629693</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>600599</t>
+          <t>598531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>667070</t>
+          <t>672695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>13963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>26977</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56911</t>
+          <t>57366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40974</t>
+          <t>43173</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75914</t>
+          <t>76950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151109</t>
+          <t>151765</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164400</t>
+          <t>164779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201868</t>
+          <t>201413</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>238238</t>
+          <t>237160</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>361607</t>
+          <t>360571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396547</t>
+          <t>394348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45604</t>
+          <t>46434</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68378</t>
+          <t>67330</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79768</t>
+          <t>80350</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103980</t>
+          <t>104020</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130895</t>
+          <t>133065</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>165214</t>
+          <t>164589</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201258</t>
+          <t>202306</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>224032</t>
+          <t>223202</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153076</t>
+          <t>153036</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>177288</t>
+          <t>176706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>361478</t>
+          <t>362103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>395797</t>
+          <t>393627</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84604</t>
+          <t>84299</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122442</t>
+          <t>123283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124896</t>
+          <t>113506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>320676</t>
+          <t>321055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>340894</t>
+          <t>340893</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>203329</t>
+          <t>229740</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>405816</t>
+          <t>406939</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>501837</t>
+          <t>500996</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>539675</t>
+          <t>539980</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>528589</t>
+          <t>528210</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>724369</t>
+          <t>735759</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1132650</t>
+          <t>1132651</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1067728</t>
+          <t>1066605</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1270215</t>
+          <t>1243804</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>84,41%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>34103</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109724</t>
+          <t>109925</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>148288</t>
+          <t>146906</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>186763</t>
+          <t>184382</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>151672</t>
+          <t>153753</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>294267</t>
+          <t>295736</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>818996</t>
+          <t>818795</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>894308</t>
+          <t>894617</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>530968</t>
+          <t>533349</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>569443</t>
+          <t>570825</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1352185</t>
+          <t>1350716</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1494780</t>
+          <t>1492699</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>360611</t>
+          <t>364903</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>516813</t>
+          <t>519297</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>772295</t>
+          <t>764091</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1028292</t>
+          <t>1028185</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1227473</t>
+          <t>1213709</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1521176</t>
+          <t>1516243</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2943004</t>
+          <t>2940520</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3099206</t>
+          <t>3094914</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2683988</t>
+          <t>2684095</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2939985</t>
+          <t>2948189</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5650921</t>
+          <t>5655854</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5944624</t>
+          <t>5958388</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DCD_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/DCD_R-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35365</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26585</t>
+          <t>26402</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47454</t>
+          <t>47692</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>53312</t>
+          <t>59418</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43691</t>
+          <t>48994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63906</t>
+          <t>70584</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>88677</t>
+          <t>95867</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74711</t>
+          <t>82253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104456</t>
+          <t>111446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>276078</t>
+          <t>282396</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263989</t>
+          <t>271153</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284858</t>
+          <t>292443</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>236323</t>
+          <t>256643</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225729</t>
+          <t>245477</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245944</t>
+          <t>267067</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>512400</t>
+          <t>539039</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>496621</t>
+          <t>523460</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>526366</t>
+          <t>552653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63358</t>
+          <t>65172</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48670</t>
+          <t>49705</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81163</t>
+          <t>85042</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>147092</t>
+          <t>153144</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130543</t>
+          <t>135691</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165480</t>
+          <t>173486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>210450</t>
+          <t>218316</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>185908</t>
+          <t>191459</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236990</t>
+          <t>248174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>455032</t>
+          <t>465475</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>437227</t>
+          <t>445605</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>469720</t>
+          <t>480942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>367877</t>
+          <t>393350</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349489</t>
+          <t>373008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>384426</t>
+          <t>410803</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>822909</t>
+          <t>858825</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>796369</t>
+          <t>828967</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>847451</t>
+          <t>885682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>56592</t>
+          <t>56435</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45370</t>
+          <t>44184</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70275</t>
+          <t>68914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>103862</t>
+          <t>105676</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92077</t>
+          <t>92348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>119303</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>160454</t>
+          <t>162111</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143681</t>
+          <t>143944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181003</t>
+          <t>179434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>259458</t>
+          <t>259558</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>245775</t>
+          <t>247079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>270680</t>
+          <t>271809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>245266</t>
+          <t>250705</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>230882</t>
+          <t>237078</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257051</t>
+          <t>264033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>504724</t>
+          <t>510264</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>484175</t>
+          <t>492941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>521497</t>
+          <t>528431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51425</t>
+          <t>55606</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39250</t>
+          <t>41837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>72180</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>107156</t>
+          <t>118408</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67062</t>
+          <t>103687</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>139108</t>
+          <t>137913</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>158581</t>
+          <t>174014</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115579</t>
+          <t>150001</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189743</t>
+          <t>197031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>261132</t>
+          <t>317539</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>245066</t>
+          <t>300965</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273307</t>
+          <t>331308</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>368562</t>
+          <t>303553</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>336610</t>
+          <t>284048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>408656</t>
+          <t>318274</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>629693</t>
+          <t>621093</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>598531</t>
+          <t>598076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672695</t>
+          <t>645106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>81,13%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>21180</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13963</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>28981</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>43327</t>
+          <t>45017</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21619</t>
+          <t>37184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57366</t>
+          <t>53751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>63347</t>
+          <t>66197</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43173</t>
+          <t>56160</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76950</t>
+          <t>77987</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>158722</t>
+          <t>184485</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151765</t>
+          <t>176684</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164779</t>
+          <t>190845</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>215452</t>
+          <t>183901</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201413</t>
+          <t>175167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>237160</t>
+          <t>191734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>374174</t>
+          <t>368385</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>360571</t>
+          <t>356595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394348</t>
+          <t>378422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>56255</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46434</t>
+          <t>46203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67330</t>
+          <t>67187</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91452</t>
+          <t>93328</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80350</t>
+          <t>81347</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104020</t>
+          <t>105935</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>147706</t>
+          <t>148932</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>133065</t>
+          <t>131653</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>164589</t>
+          <t>165225</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>213381</t>
+          <t>215103</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202306</t>
+          <t>203520</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223202</t>
+          <t>224504</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>165604</t>
+          <t>170422</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153036</t>
+          <t>157815</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>176706</t>
+          <t>182403</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>378986</t>
+          <t>385525</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>362103</t>
+          <t>369232</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>393627</t>
+          <t>402804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>103280</t>
+          <t>119774</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84299</t>
+          <t>98688</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123283</t>
+          <t>141085</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>237613</t>
+          <t>288074</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113506</t>
+          <t>263638</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>321055</t>
+          <t>312982</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>340893</t>
+          <t>407849</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>229740</t>
+          <t>373490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>406939</t>
+          <t>444489</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>520999</t>
+          <t>599913</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>500996</t>
+          <t>578602</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>539980</t>
+          <t>620999</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>611652</t>
+          <t>483983</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>528210</t>
+          <t>459075</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>735759</t>
+          <t>508419</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1132651</t>
+          <t>1083895</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1066605</t>
+          <t>1047255</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1243804</t>
+          <t>1118254</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>74,96%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>76284</t>
+          <t>86117</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34103</t>
+          <t>71687</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109925</t>
+          <t>102816</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>165731</t>
+          <t>187172</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146906</t>
+          <t>168884</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>184382</t>
+          <t>208723</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>242016</t>
+          <t>273290</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>153753</t>
+          <t>249536</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>295736</t>
+          <t>302229</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>852436</t>
+          <t>711955</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>818795</t>
+          <t>695256</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>894617</t>
+          <t>726385</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>552000</t>
+          <t>644159</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>533349</t>
+          <t>622608</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>570825</t>
+          <t>662447</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1404436</t>
+          <t>1356113</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1350716</t>
+          <t>1327174</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1492699</t>
+          <t>1379867</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>462580</t>
+          <t>496338</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>364903</t>
+          <t>457883</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>519297</t>
+          <t>543216</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>949546</t>
+          <t>1050237</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>764091</t>
+          <t>1006147</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1028185</t>
+          <t>1101531</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1412125</t>
+          <t>1546575</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1213709</t>
+          <t>1477371</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1516243</t>
+          <t>1607726</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2997237</t>
+          <t>3036424</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2940520</t>
+          <t>2989546</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3094914</t>
+          <t>3074879</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2762734</t>
+          <t>2686717</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2684095</t>
+          <t>2635423</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2948189</t>
+          <t>2730807</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5759972</t>
+          <t>5723141</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5655854</t>
+          <t>5661990</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5958388</t>
+          <t>5792345</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
